--- a/excels/BOM_FILE_2D.xlsx
+++ b/excels/BOM_FILE_2D.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\radin\Documents\Adi Heavy\Siraal\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B3712B-5110-4ABF-BAF9-389A167F47AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334E3CDB-5EB3-4C6E-B8CB-5FB3315483E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1415,7 +1415,7 @@
         <v>30</v>
       </c>
       <c r="H5" s="8">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="I5" s="8">
         <v>1</v>
